--- a/content/aptara-survey-content.xlsx
+++ b/content/aptara-survey-content.xlsx
@@ -488,7 +488,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Aptara L&amp;D Assessment: content sheet (v2, in review)</t>
+          <t>Aptara L&amp;D Assessment: content sheet (v2)</t>
         </is>
       </c>
     </row>
@@ -599,156 +599,156 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>hero_label</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>L&amp;D Assessment</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Small label above the landing headline</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>hero_headline_lead</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Discover your next</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Landing headline, first line (smaller)</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>hero_headline_main</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>L&amp;D priority.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Landing headline, main line</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>hero_subtext</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Answer five short steps about how your organization manages learning, and get practical priorities and next steps for the year ahead.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Landing page, under headline</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>start_button</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Start the assessment</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Every start button on the landing page</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>step_count_label</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>5 short steps</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>Landing page stat row</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>estimated_time</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>About 3 minutes</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>Landing page stat row (an estimate)</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -775,46 +775,46 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>result_methodology</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Your result is generated from predefined guidance using your responses, with adjustments for some answer combinations. Your maturity stage is self-reported, not a validated score. Treat this as a starting point for discussion.</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>Result page, 'How this result was generated'</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>result_scope</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>A short, self-reported assessment of how your organization manages learning, with suggested priorities and next steps.</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>Copied and printed summary, under the title</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -885,46 +885,46 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>lead_form_privacy</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>We'll send your name, work email, company and your assessment answers to Aptara's team through FormSubmit, a third-party form service, only to follow up on this request. We won't add you to marketing lists without asking.</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>Result page, next to the consent checkbox</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>privacy_policy_url</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>https://www.aptaracorp.com/privacy-and-cookie-policy/</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>Linked next to the consent checkbox and in the privacy note</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1028,300 +1028,300 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="n">
+      <c r="A3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>Maturity stage</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Which statement best describes how your organization manages learning today?</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>A directional, self-reported stage. It adjusts how much process and governance guidance the result gives. It is never inferred from team size, sourcing or delivery format.</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>How your organization manages learning today.</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
         <is>
           <t>Classification</t>
         </is>
       </c>
-      <c r="H3" s="6" t="inlineStr">
+      <c r="H3" s="5" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="I3" s="6" t="n">
+      <c r="I3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="J3" s="6" t="inlineStr"/>
-      <c r="K3" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="n">
+      <c r="A4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>Main challenge</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>What is your main L&amp;D challenge right now?</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Chooses the first priority, the title and the 30-day action.</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>The challenge that matters most right now.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="I4" s="6" t="n">
+      <c r="I4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="J4" s="6" t="inlineStr"/>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="n">
+      <c r="A5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>Delivery methods</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Which learning delivery methods do you currently use?</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Multiple selections. Tailors the delivery advice; mixed delivery gets its own guidance.</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>The delivery methods you use today.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H5" s="6" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>Multi</t>
         </is>
       </c>
-      <c r="I5" s="6" t="n">
+      <c r="I5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="J5" s="6" t="inlineStr"/>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="n">
+      <c r="A6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>Internal team</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>How many people are in your internal L&amp;D team?</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Tailors workload advice. Ranges do not overlap: 0, 1-5, 6-15, 16+.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>The size of your team and how work gets done.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr">
+      <c r="G6" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H6" s="6" t="inlineStr">
+      <c r="H6" s="5" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Your team</t>
         </is>
       </c>
-      <c r="K6" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="K6" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="n">
+      <c r="A7" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>Sourcing</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>How is your learning work delivered?</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Tailors coordination advice. Independent of team size: any combination is valid.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr">
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H7" s="6" t="inlineStr">
+      <c r="H7" s="5" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="I7" s="6" t="n">
+      <c r="I7" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Your team</t>
         </is>
       </c>
-      <c r="K7" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="K7" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="n">
+      <c r="A8" s="5" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>Business goal</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>What would you most like to improve over the next 6–12 months?</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Chooses the second priority and the 90-day action. Outcome only; never presupposes buying services.</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>What you want to improve over the next year.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr">
+      <c r="G8" s="5" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="H8" s="6" t="inlineStr">
+      <c r="H8" s="5" t="inlineStr">
         <is>
           <t>Single</t>
         </is>
       </c>
-      <c r="I8" s="6" t="n">
+      <c r="I8" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="J8" s="6" t="inlineStr"/>
-      <c r="K8" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -1395,782 +1395,782 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C3" s="6" t="n">
+      <c r="C3" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Foundational</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr">
         <is>
           <t>Learning is handled case by case, with limited shared processes.</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C4" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Developing</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>Some processes and tools are established, but consistency varies.</t>
         </is>
       </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C5" s="6" t="n">
+      <c r="C5" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Established</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr">
         <is>
           <t>Standard processes, ownership, and reporting are in place across most programs.</t>
         </is>
       </c>
-      <c r="F5" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n">
+      <c r="C6" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Optimizing</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr">
         <is>
           <t>Learning is aligned to business priorities and improved using evidence.</t>
         </is>
       </c>
-      <c r="F6" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F6" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Content upkeep</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr">
         <is>
           <t>Keeping existing learning content accurate, relevant and up to date.</t>
         </is>
       </c>
-      <c r="F7" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C8" s="6" t="n">
+      <c r="C8" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Delivery capacity</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr">
         <is>
           <t>Producing and delivering learning fast enough to meet demand.</t>
         </is>
       </c>
-      <c r="F8" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F8" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n">
+      <c r="C9" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Learner engagement</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr">
         <is>
           <t>Getting people to take part in learning and apply it at work.</t>
         </is>
       </c>
-      <c r="F9" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C10" s="6" t="n">
+      <c r="C10" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Consistent quality</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr">
         <is>
           <t>Keeping quality consistent across programs, teams or regions.</t>
         </is>
       </c>
-      <c r="F10" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F10" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C11" s="6" t="n">
+      <c r="C11" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Demonstrating impact</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr">
         <is>
           <t>Showing how learning contributes to business results.</t>
         </is>
       </c>
-      <c r="F11" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C12" s="6" t="n">
+      <c r="C12" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>In-person ILT</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>In-person instructor-led training (ILT).</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F12" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C13" s="6" t="n">
+      <c r="C13" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Virtual ILT</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Virtual instructor-led training (VILT).</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F13" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C14" s="6" t="n">
+      <c r="C14" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Self-paced eLearning</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Self-paced eLearning.</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F14" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C15" s="6" t="n">
+      <c r="C15" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Microlearning</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Microlearning or performance support, such as short videos and job aids.</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F15" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C16" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Reference materials</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Documents or reference materials.</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F16" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C17" s="6" t="n">
+      <c r="C17" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>No dedicated team</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>No dedicated internal L&amp;D team (0).</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F17" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C18" s="6" t="n">
+      <c r="C18" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Small team</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Small team (1–5 people).</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F18" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C19" s="6" t="n">
+      <c r="C19" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Medium team</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Medium team (6–15 people).</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F19" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C20" s="6" t="n">
+      <c r="C20" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Large team</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Large team (16 or more people).</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F20" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C21" s="6" t="n">
+      <c r="C21" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Mainly in-house</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Mainly in-house, by our own people.</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F21" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C22" s="6" t="n">
+      <c r="C22" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Mixed</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>By a mix of our own people and external partners.</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C23" s="6" t="n">
+      <c r="C23" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Mainly partners</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Mainly by external partners.</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="C24" s="6" t="n">
+      <c r="C24" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Delivery capacity</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Increase delivery capacity.</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="C25" s="6" t="n">
+      <c r="C25" s="5" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Faster development</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Reduce development and update time.</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="C26" s="6" t="n">
+      <c r="C26" s="5" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>Quality and consistency</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr">
         <is>
           <t>Improve learning quality and consistency.</t>
         </is>
       </c>
-      <c r="F26" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="C27" s="6" t="n">
+      <c r="C27" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Engagement and application</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr">
         <is>
           <t>Improve learner engagement and application.</t>
         </is>
       </c>
-      <c r="F27" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="C28" s="6" t="n">
+      <c r="C28" s="5" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Business impact</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr">
         <is>
           <t>Demonstrate business impact.</t>
         </is>
       </c>
-      <c r="F28" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
         </is>
       </c>
     </row>
@@ -2688,1910 +2688,1910 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Content upkeep: Keeping existing learning content accurate, relevant and up to date.</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr">
         <is>
           <t>Your next L&amp;D priority: modernize priority content</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="6">
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5">
         <f>LEN(F3)</f>
         <v/>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr"/>
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Delivery capacity: Producing and delivering learning fast enough to meet demand.</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>Your next L&amp;D priority: protect team capacity</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6">
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5">
         <f>LEN(F4)</f>
         <v/>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr"/>
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Learner engagement: Getting people to take part in learning and apply it at work.</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr">
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr">
         <is>
           <t>Your next L&amp;D priority: make learning easier to apply</t>
         </is>
       </c>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6">
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5">
         <f>LEN(F5)</f>
         <v/>
       </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr"/>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Consistent quality: Keeping quality consistent across programs, teams or regions.</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>Your next L&amp;D priority: set shared quality standards</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6">
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5">
         <f>LEN(F6)</f>
         <v/>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Demonstrating impact: Showing how learning contributes to business results.</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr">
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr">
         <is>
           <t>Your next L&amp;D priority: connect learning to business measures</t>
         </is>
       </c>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6">
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5">
         <f>LEN(F7)</f>
         <v/>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>situation</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Foundational: Learning is handled case by case, with limited shared processes.</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>You described learning in your organization as foundational: handled case by case, with limited shared processes. That is a common starting point, and a few simple, shared ways of working can make a visible difference quickly.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6">
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5">
         <f>LEN(F8)</f>
         <v/>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>situation</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Developing: Some processes and tools are established, but consistency varies.</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr">
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr">
         <is>
           <t>You described your learning practice as developing: some processes and tools are in place, but consistency varies. The opportunity is to make what already works the standard way of working.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6">
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5">
         <f>LEN(F9)</f>
         <v/>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>situation</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Established: Standard processes, ownership, and reporting are in place across most programs.</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>You described your learning practice as established, with standard processes, ownership and reporting across most programs. The focus now is less on setting things up and more on where to direct effort.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="6">
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5">
         <f>LEN(F10)</f>
         <v/>
       </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>situation</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Optimizing: Learning is aligned to business priorities and improved using evidence.</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr">
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr">
         <is>
           <t>You described your learning practice as optimizing: aligned to business priorities and improved using evidence. Your next gains are likely to come from sharper measurement and from scaling what already works.</t>
         </is>
       </c>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6">
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5">
         <f>LEN(F11)</f>
         <v/>
       </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>priority_challenge</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Content upkeep: Keeping existing learning content accurate, relevant and up to date.</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr">
         <is>
           <t>Modernize priority content</t>
         </is>
       </c>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>Identify your most-used and highest-risk content and review it first for outdated information, accessibility gaps and parts you could reuse. Give each item a review date so upkeep becomes routine.</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr">
+      <c r="G12" s="5" t="inlineStr">
         <is>
           <t>You named keeping content accurate and up to date as your main challenge.</t>
         </is>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="5">
         <f>LEN(F12)</f>
         <v/>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr"/>
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>priority_challenge</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Delivery capacity: Producing and delivering learning fast enough to meet demand.</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr">
         <is>
           <t>Protect team capacity</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>Make demand visible in one backlog, agree how requests are prioritized, and build reusable templates and patterns so each new program takes less effort.</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr">
+      <c r="G13" s="5" t="inlineStr">
         <is>
           <t>You named delivering learning fast enough to meet demand as your main challenge.</t>
         </is>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="5">
         <f>LEN(F13)</f>
         <v/>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>priority_challenge</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Learner engagement: Getting people to take part in learning and apply it at work.</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr">
         <is>
           <t>Make learning easier to apply</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Design programs around the tasks people do at work, add practice and on-the-job support, and ask managers to reinforce what was learned.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>You named getting people to take part in learning and apply it as your main challenge.</t>
         </is>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="5">
         <f>LEN(F14)</f>
         <v/>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>priority_challenge</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Consistent quality: Keeping quality consistent across programs, teams or regions.</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr">
         <is>
           <t>Set shared quality standards</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Agree a short quality checklist covering design, accuracy, accessibility and learner experience, and use it in every review, whoever builds the program.</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr">
+      <c r="G15" s="5" t="inlineStr">
         <is>
           <t>You named keeping quality consistent across programs, teams or regions as your main challenge.</t>
         </is>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="5">
         <f>LEN(F15)</f>
         <v/>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>priority_challenge</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Demonstrating impact: Showing how learning contributes to business results.</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr">
         <is>
           <t>Connect learning to business measures</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>For one or two priority programs, agree with the business owner which operational measure the program should influence, capture a baseline, and plan how you will review the change.</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr">
+      <c r="G16" s="5" t="inlineStr">
         <is>
           <t>You named showing how learning contributes to business results as your main challenge.</t>
         </is>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="5">
         <f>LEN(F16)</f>
         <v/>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Delivery capacity: Increase delivery capacity.</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr">
         <is>
           <t>Increase delivery capacity</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>Look at where time goes today, from request to launch, and remove the biggest bottlenecks before adding more programs. Reusable designs and clear sign-off steps add capacity without adding people.</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="G17" s="5" t="inlineStr">
         <is>
           <t>You chose increasing delivery capacity as your goal for the next 6–12 months.</t>
         </is>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="5">
         <f>LEN(F17)</f>
         <v/>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr"/>
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Faster development: Reduce development and update time.</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr">
         <is>
           <t>Shorten development and update time</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>Build a library of reusable templates, components and examples, and keep source files organized so updates are quicker to make.</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>You chose reducing development and update time as your goal for the next 6–12 months.</t>
         </is>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="5">
         <f>LEN(F18)</f>
         <v/>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr"/>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Quality and consistency: Improve learning quality and consistency.</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr">
         <is>
           <t>Raise quality and consistency</t>
         </is>
       </c>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>Define what good looks like for your programs, share it with everyone who builds or reviews learning, and check a sample of programs against it each quarter.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>You chose improving learning quality and consistency as your goal for the next 6–12 months.</t>
         </is>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="5">
         <f>LEN(F19)</f>
         <v/>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr"/>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Engagement and application: Improve learner engagement and application.</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr">
         <is>
           <t>Strengthen engagement and application</t>
         </is>
       </c>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Choose one program and add practice, reminders and manager follow-up after it, then compare participation and feedback with earlier runs.</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>You chose improving learner engagement and application as your goal for the next 6–12 months.</t>
         </is>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="5">
         <f>LEN(F20)</f>
         <v/>
       </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Business impact: Demonstrate business impact.</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr">
         <is>
           <t>Demonstrate business impact</t>
         </is>
       </c>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Choose a small number of programs where a business outcome can reasonably be linked to learning, and agree with stakeholders how results will be evaluated and reported.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>You chose demonstrating business impact as your goal for the next 6–12 months.</t>
         </is>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="5">
         <f>LEN(F21)</f>
         <v/>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr"/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>priority_process</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Foundational: Learning is handled case by case, with limited shared processes.</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr">
         <is>
           <t>Agree a simple intake process</t>
         </is>
       </c>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Set up one shared way to request, prioritize and track learning work, with a named owner for each program. Even a lightweight process makes demand visible and decisions easier.</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr">
+      <c r="G22" s="5" t="inlineStr">
         <is>
           <t>You said learning is handled case by case, so a shared process is the foundation the other priorities depend on.</t>
         </is>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="5">
         <f>LEN(F22)</f>
         <v/>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>priority_process</t>
         </is>
       </c>
-      <c r="B23" s="6" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C23" s="6" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>Developing: Some processes and tools are established, but consistency varies.</t>
         </is>
       </c>
-      <c r="E23" s="6" t="inlineStr">
+      <c r="E23" s="5" t="inlineStr">
         <is>
           <t>Standardize what already works</t>
         </is>
       </c>
-      <c r="F23" s="6" t="inlineStr">
+      <c r="F23" s="5" t="inlineStr">
         <is>
           <t>Pick the processes and templates that work best today and make them the default for new programs, with a short checklist for design and review.</t>
         </is>
       </c>
-      <c r="G23" s="6" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>You said consistency varies, so standardizing proven practices reduces rework without adding much overhead.</t>
         </is>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="5">
         <f>LEN(F23)</f>
         <v/>
       </c>
-      <c r="I23" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J23" s="6" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="6" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>priority_process</t>
         </is>
       </c>
-      <c r="B24" s="6" t="inlineStr">
+      <c r="B24" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C24" s="6" t="inlineStr">
+      <c r="C24" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="5" t="inlineStr">
         <is>
           <t>Established: Standard processes, ownership, and reporting are in place across most programs.</t>
         </is>
       </c>
-      <c r="E24" s="6" t="inlineStr">
+      <c r="E24" s="5" t="inlineStr">
         <is>
           <t>Focus effort where it counts</t>
         </is>
       </c>
-      <c r="F24" s="6" t="inlineStr">
+      <c r="F24" s="5" t="inlineStr">
         <is>
           <t>Review your portfolio against current business priorities, and retire or refresh programs that no longer earn their place. Use your existing reporting to decide where to invest.</t>
         </is>
       </c>
-      <c r="G24" s="6" t="inlineStr">
+      <c r="G24" s="5" t="inlineStr">
         <is>
           <t>With standard processes and reporting in place, the biggest gains come from where you direct effort.</t>
         </is>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="5">
         <f>LEN(F24)</f>
         <v/>
       </c>
-      <c r="I24" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J24" s="6" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="6" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>priority_process</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B25" s="5" t="inlineStr">
         <is>
           <t>Q1</t>
         </is>
       </c>
-      <c r="C25" s="6" t="inlineStr">
+      <c r="C25" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="5" t="inlineStr">
         <is>
           <t>Optimizing: Learning is aligned to business priorities and improved using evidence.</t>
         </is>
       </c>
-      <c r="E25" s="6" t="inlineStr">
+      <c r="E25" s="5" t="inlineStr">
         <is>
           <t>Scale what the evidence supports</t>
         </is>
       </c>
-      <c r="F25" s="6" t="inlineStr">
+      <c r="F25" s="5" t="inlineStr">
         <is>
           <t>Use the evidence you already collect to find the programs with the clearest results, and apply their design patterns more widely.</t>
         </is>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="G25" s="5" t="inlineStr">
         <is>
           <t>You said learning is already improved using evidence, so the next step is to spread what works rather than add new process.</t>
         </is>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="5">
         <f>LEN(F25)</f>
         <v/>
       </c>
-      <c r="I25" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J25" s="6" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="6" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B26" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C26" s="6" t="inlineStr">
+      <c r="C26" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="5" t="inlineStr">
         <is>
           <t>In-person ILT: In-person instructor-led training (ILT).</t>
         </is>
       </c>
-      <c r="E26" s="6" t="inlineStr"/>
-      <c r="F26" s="6" t="inlineStr">
+      <c r="E26" s="5" t="inlineStr"/>
+      <c r="F26" s="5" t="inlineStr">
         <is>
           <t>You deliver learning through in-person sessions. Consider which parts could be supported with short reference materials or follow-up activities, so learning continues after the session.</t>
         </is>
       </c>
-      <c r="G26" s="6" t="inlineStr"/>
-      <c r="H26" s="6">
+      <c r="G26" s="5" t="inlineStr"/>
+      <c r="H26" s="5">
         <f>LEN(F26)</f>
         <v/>
       </c>
-      <c r="I26" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J26" s="6" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="6" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B27" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C27" s="6" t="inlineStr">
+      <c r="C27" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D27" s="6" t="inlineStr">
+      <c r="D27" s="5" t="inlineStr">
         <is>
           <t>Virtual ILT: Virtual instructor-led training (VILT).</t>
         </is>
       </c>
-      <c r="E27" s="6" t="inlineStr"/>
-      <c r="F27" s="6" t="inlineStr">
+      <c r="E27" s="5" t="inlineStr"/>
+      <c r="F27" s="5" t="inlineStr">
         <is>
           <t>You deliver learning through virtual live sessions. Keep sessions interactive and focused, and add simple follow-up materials so people can revisit key points.</t>
         </is>
       </c>
-      <c r="G27" s="6" t="inlineStr"/>
-      <c r="H27" s="6">
+      <c r="G27" s="5" t="inlineStr"/>
+      <c r="H27" s="5">
         <f>LEN(F27)</f>
         <v/>
       </c>
-      <c r="I27" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J27" s="6" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="6" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="B28" s="6" t="inlineStr">
+      <c r="B28" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C28" s="6" t="inlineStr">
+      <c r="C28" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="5" t="inlineStr">
         <is>
           <t>Self-paced eLearning: Self-paced eLearning.</t>
         </is>
       </c>
-      <c r="E28" s="6" t="inlineStr"/>
-      <c r="F28" s="6" t="inlineStr">
+      <c r="E28" s="5" t="inlineStr"/>
+      <c r="F28" s="5" t="inlineStr">
         <is>
           <t>You use self-paced eLearning. Review your most-used modules regularly for outdated examples and accessibility gaps, and look for content you could reuse across courses.</t>
         </is>
       </c>
-      <c r="G28" s="6" t="inlineStr"/>
-      <c r="H28" s="6">
+      <c r="G28" s="5" t="inlineStr"/>
+      <c r="H28" s="5">
         <f>LEN(F28)</f>
         <v/>
       </c>
-      <c r="I28" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J28" s="6" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="6" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="B29" s="6" t="inlineStr">
+      <c r="B29" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C29" s="6" t="inlineStr">
+      <c r="C29" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D29" s="6" t="inlineStr">
+      <c r="D29" s="5" t="inlineStr">
         <is>
           <t>Microlearning: Microlearning or performance support, such as short videos and job aids.</t>
         </is>
       </c>
-      <c r="E29" s="6" t="inlineStr"/>
-      <c r="F29" s="6" t="inlineStr">
+      <c r="E29" s="5" t="inlineStr"/>
+      <c r="F29" s="5" t="inlineStr">
         <is>
           <t>You use microlearning and performance support. Make sure each resource is easy to find at the moment of need, and link related resources so they support a bigger goal.</t>
         </is>
       </c>
-      <c r="G29" s="6" t="inlineStr"/>
-      <c r="H29" s="6">
+      <c r="G29" s="5" t="inlineStr"/>
+      <c r="H29" s="5">
         <f>LEN(F29)</f>
         <v/>
       </c>
-      <c r="I29" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J29" s="6" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="6" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="B30" s="6" t="inlineStr">
+      <c r="B30" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C30" s="6" t="inlineStr">
+      <c r="C30" s="5" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D30" s="6" t="inlineStr">
+      <c r="D30" s="5" t="inlineStr">
         <is>
           <t>Reference materials: Documents or reference materials.</t>
         </is>
       </c>
-      <c r="E30" s="6" t="inlineStr"/>
-      <c r="F30" s="6" t="inlineStr">
+      <c r="E30" s="5" t="inlineStr"/>
+      <c r="F30" s="5" t="inlineStr">
         <is>
           <t>You use documents and reference materials. Keep them current, easy to search and clearly owned, and consider which topics would benefit from practice or guided learning.</t>
         </is>
       </c>
-      <c r="G30" s="6" t="inlineStr"/>
-      <c r="H30" s="6">
+      <c r="G30" s="5" t="inlineStr"/>
+      <c r="H30" s="5">
         <f>LEN(F30)</f>
         <v/>
       </c>
-      <c r="I30" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J30" s="6" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="B31" s="6" t="inlineStr">
+      <c r="B31" s="5" t="inlineStr">
         <is>
           <t>Q3</t>
         </is>
       </c>
-      <c r="C31" s="6" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>MULTI</t>
         </is>
       </c>
-      <c r="D31" s="6" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Several selected (MULTI)</t>
         </is>
       </c>
-      <c r="E31" s="6" t="inlineStr"/>
-      <c r="F31" s="6" t="inlineStr">
+      <c r="E31" s="5" t="inlineStr"/>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>You use several delivery methods: {Q3}. Identify where they can work together to support the same outcome, rather than planning each one separately.</t>
         </is>
       </c>
-      <c r="G31" s="6" t="inlineStr"/>
-      <c r="H31" s="6">
+      <c r="G31" s="5" t="inlineStr"/>
+      <c r="H31" s="5">
         <f>LEN(F31)</f>
         <v/>
       </c>
-      <c r="I31" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J31" s="6" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="6" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B32" s="6" t="inlineStr">
+      <c r="B32" s="5" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C32" s="6" t="inlineStr">
+      <c r="C32" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D32" s="6" t="inlineStr">
+      <c r="D32" s="5" t="inlineStr">
         <is>
           <t>No dedicated team: No dedicated internal L&amp;D team (0).</t>
         </is>
       </c>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="6" t="inlineStr">
+      <c r="E32" s="5" t="inlineStr"/>
+      <c r="F32" s="5" t="inlineStr">
         <is>
           <t>You don't have a dedicated internal L&amp;D team, so clear ownership matters most: name who decides priorities and who signs off learning content, even when it is part of a wider role.</t>
         </is>
       </c>
-      <c r="G32" s="6" t="inlineStr"/>
-      <c r="H32" s="6">
+      <c r="G32" s="5" t="inlineStr"/>
+      <c r="H32" s="5">
         <f>LEN(F32)</f>
         <v/>
       </c>
-      <c r="I32" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J32" s="6" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="6" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B33" s="6" t="inlineStr">
+      <c r="B33" s="5" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C33" s="6" t="inlineStr">
+      <c r="C33" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
+      <c r="D33" s="5" t="inlineStr">
         <is>
           <t>Small team: Small team (1–5 people).</t>
         </is>
       </c>
-      <c r="E33" s="6" t="inlineStr"/>
-      <c r="F33" s="6" t="inlineStr">
+      <c r="E33" s="5" t="inlineStr"/>
+      <c r="F33" s="5" t="inlineStr">
         <is>
           <t>With a small team, prioritize a manageable backlog and reusable patterns to protect delivery capacity.</t>
         </is>
       </c>
-      <c r="G33" s="6" t="inlineStr"/>
-      <c r="H33" s="6">
+      <c r="G33" s="5" t="inlineStr"/>
+      <c r="H33" s="5">
         <f>LEN(F33)</f>
         <v/>
       </c>
-      <c r="I33" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J33" s="6" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="6" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B34" s="6" t="inlineStr">
+      <c r="B34" s="5" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C34" s="6" t="inlineStr">
+      <c r="C34" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D34" s="6" t="inlineStr">
+      <c r="D34" s="5" t="inlineStr">
         <is>
           <t>Medium team: Medium team (6–15 people).</t>
         </is>
       </c>
-      <c r="E34" s="6" t="inlineStr"/>
-      <c r="F34" s="6" t="inlineStr">
+      <c r="E34" s="5" t="inlineStr"/>
+      <c r="F34" s="5" t="inlineStr">
         <is>
           <t>With a medium-sized team, agree shared standards and clear handoffs so work stays consistent as it moves between people.</t>
         </is>
       </c>
-      <c r="G34" s="6" t="inlineStr"/>
-      <c r="H34" s="6">
+      <c r="G34" s="5" t="inlineStr"/>
+      <c r="H34" s="5">
         <f>LEN(F34)</f>
         <v/>
       </c>
-      <c r="I34" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J34" s="6" t="inlineStr"/>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J34" s="5" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="6" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="B35" s="6" t="inlineStr">
+      <c r="B35" s="5" t="inlineStr">
         <is>
           <t>Q4</t>
         </is>
       </c>
-      <c r="C35" s="6" t="inlineStr">
+      <c r="C35" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
+      <c r="D35" s="5" t="inlineStr">
         <is>
           <t>Large team: Large team (16 or more people).</t>
         </is>
       </c>
-      <c r="E35" s="6" t="inlineStr"/>
-      <c r="F35" s="6" t="inlineStr">
+      <c r="E35" s="5" t="inlineStr"/>
+      <c r="F35" s="5" t="inlineStr">
         <is>
           <t>With a large team, make roles, review ownership and standards clear across groups so effort isn't duplicated.</t>
         </is>
       </c>
-      <c r="G35" s="6" t="inlineStr"/>
-      <c r="H35" s="6">
+      <c r="G35" s="5" t="inlineStr"/>
+      <c r="H35" s="5">
         <f>LEN(F35)</f>
         <v/>
       </c>
-      <c r="I35" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J35" s="6" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J35" s="5" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="6" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>sourcing</t>
         </is>
       </c>
-      <c r="B36" s="6" t="inlineStr">
+      <c r="B36" s="5" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C36" s="6" t="inlineStr">
+      <c r="C36" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D36" s="6" t="inlineStr">
+      <c r="D36" s="5" t="inlineStr">
         <is>
           <t>Mainly in-house: Mainly in-house, by our own people.</t>
         </is>
       </c>
-      <c r="E36" s="6" t="inlineStr"/>
-      <c r="F36" s="6" t="inlineStr">
+      <c r="E36" s="5" t="inlineStr"/>
+      <c r="F36" s="5" t="inlineStr">
         <is>
           <t>Because most work is done in-house, document key processes and decisions so knowledge isn't held by only a few people.</t>
         </is>
       </c>
-      <c r="G36" s="6" t="inlineStr"/>
-      <c r="H36" s="6">
+      <c r="G36" s="5" t="inlineStr"/>
+      <c r="H36" s="5">
         <f>LEN(F36)</f>
         <v/>
       </c>
-      <c r="I36" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J36" s="6" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J36" s="5" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>sourcing</t>
         </is>
       </c>
-      <c r="B37" s="6" t="inlineStr">
+      <c r="B37" s="5" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C37" s="6" t="inlineStr">
+      <c r="C37" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D37" s="6" t="inlineStr">
+      <c r="D37" s="5" t="inlineStr">
         <is>
           <t>Mixed: By a mix of our own people and external partners.</t>
         </is>
       </c>
-      <c r="E37" s="6" t="inlineStr"/>
-      <c r="F37" s="6" t="inlineStr">
+      <c r="E37" s="5" t="inlineStr"/>
+      <c r="F37" s="5" t="inlineStr">
         <is>
           <t>With work shared between your own people and partners, agree briefs, review steps and quality standards that both sides use.</t>
         </is>
       </c>
-      <c r="G37" s="6" t="inlineStr"/>
-      <c r="H37" s="6">
+      <c r="G37" s="5" t="inlineStr"/>
+      <c r="H37" s="5">
         <f>LEN(F37)</f>
         <v/>
       </c>
-      <c r="I37" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J37" s="6" t="inlineStr"/>
+      <c r="I37" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J37" s="5" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="6" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>sourcing</t>
         </is>
       </c>
-      <c r="B38" s="6" t="inlineStr">
+      <c r="B38" s="5" t="inlineStr">
         <is>
           <t>Q5</t>
         </is>
       </c>
-      <c r="C38" s="6" t="inlineStr">
+      <c r="C38" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D38" s="6" t="inlineStr">
+      <c r="D38" s="5" t="inlineStr">
         <is>
           <t>Mainly partners: Mainly by external partners.</t>
         </is>
       </c>
-      <c r="E38" s="6" t="inlineStr"/>
-      <c r="F38" s="6" t="inlineStr">
+      <c r="E38" s="5" t="inlineStr"/>
+      <c r="F38" s="5" t="inlineStr">
         <is>
           <t>As partners deliver most of the work, keep ownership of priorities, quality standards and final sign-off inside your organization.</t>
         </is>
       </c>
-      <c r="G38" s="6" t="inlineStr"/>
-      <c r="H38" s="6">
+      <c r="G38" s="5" t="inlineStr"/>
+      <c r="H38" s="5">
         <f>LEN(F38)</f>
         <v/>
       </c>
-      <c r="I38" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J38" s="6" t="inlineStr"/>
+      <c r="I38" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J38" s="5" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="6" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>next30</t>
         </is>
       </c>
-      <c r="B39" s="6" t="inlineStr">
+      <c r="B39" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C39" s="6" t="inlineStr">
+      <c r="C39" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D39" s="6" t="inlineStr">
+      <c r="D39" s="5" t="inlineStr">
         <is>
           <t>Content upkeep: Keeping existing learning content accurate, relevant and up to date.</t>
         </is>
       </c>
-      <c r="E39" s="6" t="inlineStr"/>
-      <c r="F39" s="6" t="inlineStr">
+      <c r="E39" s="5" t="inlineStr"/>
+      <c r="F39" s="5" t="inlineStr">
         <is>
           <t>List your most-used learning assets and note when each was last reviewed. Pick the two most out of date and schedule their review.</t>
         </is>
       </c>
-      <c r="G39" s="6" t="inlineStr"/>
-      <c r="H39" s="6">
+      <c r="G39" s="5" t="inlineStr"/>
+      <c r="H39" s="5">
         <f>LEN(F39)</f>
         <v/>
       </c>
-      <c r="I39" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J39" s="6" t="inlineStr"/>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J39" s="5" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="6" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>next30</t>
         </is>
       </c>
-      <c r="B40" s="6" t="inlineStr">
+      <c r="B40" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C40" s="6" t="inlineStr">
+      <c r="C40" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D40" s="6" t="inlineStr">
+      <c r="D40" s="5" t="inlineStr">
         <is>
           <t>Delivery capacity: Producing and delivering learning fast enough to meet demand.</t>
         </is>
       </c>
-      <c r="E40" s="6" t="inlineStr"/>
-      <c r="F40" s="6" t="inlineStr">
+      <c r="E40" s="5" t="inlineStr"/>
+      <c r="F40" s="5" t="inlineStr">
         <is>
           <t>Put every open learning request into one list with a requester, a deadline and a business reason, and agree the top priorities with stakeholders.</t>
         </is>
       </c>
-      <c r="G40" s="6" t="inlineStr"/>
-      <c r="H40" s="6">
+      <c r="G40" s="5" t="inlineStr"/>
+      <c r="H40" s="5">
         <f>LEN(F40)</f>
         <v/>
       </c>
-      <c r="I40" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J40" s="6" t="inlineStr"/>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J40" s="5" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="6" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>next30</t>
         </is>
       </c>
-      <c r="B41" s="6" t="inlineStr">
+      <c r="B41" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C41" s="6" t="inlineStr">
+      <c r="C41" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D41" s="6" t="inlineStr">
+      <c r="D41" s="5" t="inlineStr">
         <is>
           <t>Learner engagement: Getting people to take part in learning and apply it at work.</t>
         </is>
       </c>
-      <c r="E41" s="6" t="inlineStr"/>
-      <c r="F41" s="6" t="inlineStr">
+      <c r="E41" s="5" t="inlineStr"/>
+      <c r="F41" s="5" t="inlineStr">
         <is>
           <t>Ask a few recent participants and their managers what they have used at work since the program, and note what got in the way.</t>
         </is>
       </c>
-      <c r="G41" s="6" t="inlineStr"/>
-      <c r="H41" s="6">
+      <c r="G41" s="5" t="inlineStr"/>
+      <c r="H41" s="5">
         <f>LEN(F41)</f>
         <v/>
       </c>
-      <c r="I41" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J41" s="6" t="inlineStr"/>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J41" s="5" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="6" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>next30</t>
         </is>
       </c>
-      <c r="B42" s="6" t="inlineStr">
+      <c r="B42" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C42" s="6" t="inlineStr">
+      <c r="C42" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D42" s="5" t="inlineStr">
         <is>
           <t>Consistent quality: Keeping quality consistent across programs, teams or regions.</t>
         </is>
       </c>
-      <c r="E42" s="6" t="inlineStr"/>
-      <c r="F42" s="6" t="inlineStr">
+      <c r="E42" s="5" t="inlineStr"/>
+      <c r="F42" s="5" t="inlineStr">
         <is>
           <t>Draft a one-page quality checklist and test it on two recent programs, ideally built by different people or partners.</t>
         </is>
       </c>
-      <c r="G42" s="6" t="inlineStr"/>
-      <c r="H42" s="6">
+      <c r="G42" s="5" t="inlineStr"/>
+      <c r="H42" s="5">
         <f>LEN(F42)</f>
         <v/>
       </c>
-      <c r="I42" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="inlineStr"/>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J42" s="5" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="6" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>next30</t>
         </is>
       </c>
-      <c r="B43" s="6" t="inlineStr">
+      <c r="B43" s="5" t="inlineStr">
         <is>
           <t>Q2</t>
         </is>
       </c>
-      <c r="C43" s="6" t="inlineStr">
+      <c r="C43" s="5" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D43" s="6" t="inlineStr">
+      <c r="D43" s="5" t="inlineStr">
         <is>
           <t>Demonstrating impact: Showing how learning contributes to business results.</t>
         </is>
       </c>
-      <c r="E43" s="6" t="inlineStr"/>
-      <c r="F43" s="6" t="inlineStr">
+      <c r="E43" s="5" t="inlineStr"/>
+      <c r="F43" s="5" t="inlineStr">
         <is>
           <t>Pick one priority program and agree with its business owner which measure it should influence and where the data will come from.</t>
         </is>
       </c>
-      <c r="G43" s="6" t="inlineStr"/>
-      <c r="H43" s="6">
+      <c r="G43" s="5" t="inlineStr"/>
+      <c r="H43" s="5">
         <f>LEN(F43)</f>
         <v/>
       </c>
-      <c r="I43" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="inlineStr"/>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J43" s="5" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="6" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>next90</t>
         </is>
       </c>
-      <c r="B44" s="6" t="inlineStr">
+      <c r="B44" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C44" s="6" t="inlineStr">
+      <c r="C44" s="5" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="5" t="inlineStr">
         <is>
           <t>Delivery capacity: Increase delivery capacity.</t>
         </is>
       </c>
-      <c r="E44" s="6" t="inlineStr"/>
-      <c r="F44" s="6" t="inlineStr">
+      <c r="E44" s="5" t="inlineStr"/>
+      <c r="F44" s="5" t="inlineStr">
         <is>
           <t>Map how a typical program moves from request to launch, remove the biggest bottleneck, and create reusable templates for your most common requests.</t>
         </is>
       </c>
-      <c r="G44" s="6" t="inlineStr"/>
-      <c r="H44" s="6">
+      <c r="G44" s="5" t="inlineStr"/>
+      <c r="H44" s="5">
         <f>LEN(F44)</f>
         <v/>
       </c>
-      <c r="I44" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J44" s="6" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J44" s="5" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="6" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>next90</t>
         </is>
       </c>
-      <c r="B45" s="6" t="inlineStr">
+      <c r="B45" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C45" s="6" t="inlineStr">
+      <c r="C45" s="5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="D45" s="6" t="inlineStr">
+      <c r="D45" s="5" t="inlineStr">
         <is>
           <t>Faster development: Reduce development and update time.</t>
         </is>
       </c>
-      <c r="E45" s="6" t="inlineStr"/>
-      <c r="F45" s="6" t="inlineStr">
+      <c r="E45" s="5" t="inlineStr"/>
+      <c r="F45" s="5" t="inlineStr">
         <is>
           <t>Build a shared library of templates and reusable components, and organize source files so any program can be updated quickly.</t>
         </is>
       </c>
-      <c r="G45" s="6" t="inlineStr"/>
-      <c r="H45" s="6">
+      <c r="G45" s="5" t="inlineStr"/>
+      <c r="H45" s="5">
         <f>LEN(F45)</f>
         <v/>
       </c>
-      <c r="I45" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J45" s="6" t="inlineStr"/>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J45" s="5" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="6" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>next90</t>
         </is>
       </c>
-      <c r="B46" s="6" t="inlineStr">
+      <c r="B46" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C46" s="6" t="inlineStr">
+      <c r="C46" s="5" t="inlineStr">
         <is>
           <t>C</t>
         </is>
       </c>
-      <c r="D46" s="6" t="inlineStr">
+      <c r="D46" s="5" t="inlineStr">
         <is>
           <t>Quality and consistency: Improve learning quality and consistency.</t>
         </is>
       </c>
-      <c r="E46" s="6" t="inlineStr"/>
-      <c r="F46" s="6" t="inlineStr">
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="5" t="inlineStr">
         <is>
           <t>Roll out a quality checklist to everyone who builds or reviews learning, and review a sample of programs against it at the end of the quarter.</t>
         </is>
       </c>
-      <c r="G46" s="6" t="inlineStr"/>
-      <c r="H46" s="6">
+      <c r="G46" s="5" t="inlineStr"/>
+      <c r="H46" s="5">
         <f>LEN(F46)</f>
         <v/>
       </c>
-      <c r="I46" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J46" s="6" t="inlineStr"/>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J46" s="5" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="6" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>next90</t>
         </is>
       </c>
-      <c r="B47" s="6" t="inlineStr">
+      <c r="B47" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C47" s="6" t="inlineStr">
+      <c r="C47" s="5" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="D47" s="6" t="inlineStr">
+      <c r="D47" s="5" t="inlineStr">
         <is>
           <t>Engagement and application: Improve learner engagement and application.</t>
         </is>
       </c>
-      <c r="E47" s="6" t="inlineStr"/>
-      <c r="F47" s="6" t="inlineStr">
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="5" t="inlineStr">
         <is>
           <t>Redesign one program with practice activities and manager follow-up, then compare participation, feedback and application with the previous version.</t>
         </is>
       </c>
-      <c r="G47" s="6" t="inlineStr"/>
-      <c r="H47" s="6">
+      <c r="G47" s="5" t="inlineStr"/>
+      <c r="H47" s="5">
         <f>LEN(F47)</f>
         <v/>
       </c>
-      <c r="I47" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J47" s="6" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J47" s="5" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="6" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>next90</t>
         </is>
       </c>
-      <c r="B48" s="6" t="inlineStr">
+      <c r="B48" s="5" t="inlineStr">
         <is>
           <t>Q6</t>
         </is>
       </c>
-      <c r="C48" s="6" t="inlineStr">
+      <c r="C48" s="5" t="inlineStr">
         <is>
           <t>E</t>
         </is>
       </c>
-      <c r="D48" s="6" t="inlineStr">
+      <c r="D48" s="5" t="inlineStr">
         <is>
           <t>Business impact: Demonstrate business impact.</t>
         </is>
       </c>
-      <c r="E48" s="6" t="inlineStr"/>
-      <c r="F48" s="6" t="inlineStr">
+      <c r="E48" s="5" t="inlineStr"/>
+      <c r="F48" s="5" t="inlineStr">
         <is>
           <t>Share the results of one evaluated program with its business owner, agree what the evidence does and doesn't show, and decide which program to evaluate next.</t>
         </is>
       </c>
-      <c r="G48" s="6" t="inlineStr"/>
-      <c r="H48" s="6">
+      <c r="G48" s="5" t="inlineStr"/>
+      <c r="H48" s="5">
         <f>LEN(F48)</f>
         <v/>
       </c>
-      <c r="I48" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J48" s="6" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J48" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4687,820 +4687,820 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>R01</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B3" s="5" t="inlineStr">
         <is>
           <t>Q2=A AND Q6=B</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C3" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="5" t="inlineStr">
         <is>
           <t>Remove</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr"/>
-      <c r="F3" s="6" t="inlineStr"/>
-      <c r="G3" s="6" t="inlineStr"/>
-      <c r="H3" s="6" t="n">
+      <c r="E3" s="5" t="inlineStr"/>
+      <c r="F3" s="5" t="inlineStr"/>
+      <c r="G3" s="5" t="inlineStr"/>
+      <c r="H3" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I3" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="I3" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J3" s="5" t="inlineStr">
         <is>
           <t>Content upkeep and faster updates are the same priority; show it once.</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>R02</t>
         </is>
       </c>
-      <c r="B4" s="6" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>Q2=A AND Q6=B</t>
         </is>
       </c>
-      <c r="C4" s="6" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>priority_challenge</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E4" s="6" t="inlineStr"/>
-      <c r="F4" s="6" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr"/>
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>This is also the goal you set for the next 6–12 months, so it is listed once.</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr"/>
-      <c r="H4" s="6" t="n">
+      <c r="G4" s="5" t="inlineStr"/>
+      <c r="H4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
         <is>
           <t>Explains why the goal priority is missing.</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>R03</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>Q2=B AND Q6=A</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="D5" s="6" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>Remove</t>
         </is>
       </c>
-      <c r="E5" s="6" t="inlineStr"/>
-      <c r="F5" s="6" t="inlineStr"/>
-      <c r="G5" s="6" t="inlineStr"/>
-      <c r="H5" s="6" t="n">
+      <c r="E5" s="5" t="inlineStr"/>
+      <c r="F5" s="5" t="inlineStr"/>
+      <c r="G5" s="5" t="inlineStr"/>
+      <c r="H5" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
         <is>
           <t>Delivery capacity challenge and goal are the same priority.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>R04</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>Q2=B AND Q6=A</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="5" t="inlineStr">
         <is>
           <t>priority_challenge</t>
         </is>
       </c>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E6" s="6" t="inlineStr"/>
-      <c r="F6" s="6" t="inlineStr">
+      <c r="E6" s="5" t="inlineStr"/>
+      <c r="F6" s="5" t="inlineStr">
         <is>
           <t>This is also the goal you set for the next 6–12 months, so it is listed once.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="inlineStr"/>
-      <c r="H6" s="6" t="n">
+      <c r="G6" s="5" t="inlineStr"/>
+      <c r="H6" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I6" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="inlineStr">
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J6" s="5" t="inlineStr">
         <is>
           <t>Explains why the goal priority is missing.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>R05</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>Q2=C AND Q6=D</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="5" t="inlineStr">
         <is>
           <t>Remove</t>
         </is>
       </c>
-      <c r="E7" s="6" t="inlineStr"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
-      <c r="H7" s="6" t="n">
+      <c r="E7" s="5" t="inlineStr"/>
+      <c r="F7" s="5" t="inlineStr"/>
+      <c r="G7" s="5" t="inlineStr"/>
+      <c r="H7" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J7" s="5" t="inlineStr">
         <is>
           <t>Engagement challenge and goal are the same priority.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>R06</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="5" t="inlineStr">
         <is>
           <t>Q2=C AND Q6=D</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="5" t="inlineStr">
         <is>
           <t>priority_challenge</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E8" s="6" t="inlineStr"/>
-      <c r="F8" s="6" t="inlineStr">
+      <c r="E8" s="5" t="inlineStr"/>
+      <c r="F8" s="5" t="inlineStr">
         <is>
           <t>This is also the goal you set for the next 6–12 months, so it is listed once.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="inlineStr"/>
-      <c r="H8" s="6" t="n">
+      <c r="G8" s="5" t="inlineStr"/>
+      <c r="H8" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>Explains why the goal priority is missing.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>R07</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="5" t="inlineStr">
         <is>
           <t>Q2=D AND Q6=C</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="5" t="inlineStr">
         <is>
           <t>Remove</t>
         </is>
       </c>
-      <c r="E9" s="6" t="inlineStr"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
-      <c r="H9" s="6" t="n">
+      <c r="E9" s="5" t="inlineStr"/>
+      <c r="F9" s="5" t="inlineStr"/>
+      <c r="G9" s="5" t="inlineStr"/>
+      <c r="H9" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
         <is>
           <t>Quality challenge and goal are the same priority.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>R08</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="5" t="inlineStr">
         <is>
           <t>Q2=D AND Q6=C</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="5" t="inlineStr">
         <is>
           <t>priority_challenge</t>
         </is>
       </c>
-      <c r="D10" s="6" t="inlineStr">
+      <c r="D10" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E10" s="6" t="inlineStr"/>
-      <c r="F10" s="6" t="inlineStr">
+      <c r="E10" s="5" t="inlineStr"/>
+      <c r="F10" s="5" t="inlineStr">
         <is>
           <t>This is also the goal you set for the next 6–12 months, so it is listed once.</t>
         </is>
       </c>
-      <c r="G10" s="6" t="inlineStr"/>
-      <c r="H10" s="6" t="n">
+      <c r="G10" s="5" t="inlineStr"/>
+      <c r="H10" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J10" s="6" t="inlineStr">
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
         <is>
           <t>Explains why the goal priority is missing.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>R09</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="5" t="inlineStr">
         <is>
           <t>Q2=E AND Q6=E</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="D11" s="6" t="inlineStr">
+      <c r="D11" s="5" t="inlineStr">
         <is>
           <t>Remove</t>
         </is>
       </c>
-      <c r="E11" s="6" t="inlineStr"/>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="6" t="inlineStr"/>
-      <c r="H11" s="6" t="n">
+      <c r="E11" s="5" t="inlineStr"/>
+      <c r="F11" s="5" t="inlineStr"/>
+      <c r="G11" s="5" t="inlineStr"/>
+      <c r="H11" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="inlineStr">
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
         <is>
           <t>Impact challenge and goal are the same priority.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>R10</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>Q2=E AND Q6=E</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="5" t="inlineStr">
         <is>
           <t>priority_challenge</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E12" s="6" t="inlineStr"/>
-      <c r="F12" s="6" t="inlineStr">
+      <c r="E12" s="5" t="inlineStr"/>
+      <c r="F12" s="5" t="inlineStr">
         <is>
           <t>This is also the goal you set for the next 6–12 months, so it is listed once.</t>
         </is>
       </c>
-      <c r="G12" s="6" t="inlineStr"/>
-      <c r="H12" s="6" t="n">
+      <c r="G12" s="5" t="inlineStr"/>
+      <c r="H12" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J12" s="6" t="inlineStr">
+      <c r="I12" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
         <is>
           <t>Explains why the goal priority is missing.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>R11</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="5" t="inlineStr">
         <is>
           <t>Q2=A AND Q3=C</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="5" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr"/>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="E13" s="5" t="inlineStr"/>
+      <c r="F13" s="5" t="inlineStr">
         <is>
           <t>As content upkeep is your main challenge, start with your highest-use eLearning: check for outdated examples, accessibility gaps and reusable content.</t>
         </is>
       </c>
-      <c r="G13" s="6" t="inlineStr"/>
-      <c r="H13" s="6" t="n">
+      <c r="G13" s="5" t="inlineStr"/>
+      <c r="H13" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="inlineStr">
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>eLearning user with content upkeep challenge.</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>R12</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>Q2=A AND Q3=E</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr"/>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="E14" s="5" t="inlineStr"/>
+      <c r="F14" s="5" t="inlineStr">
         <is>
           <t>Give each reference document an owner and a review date, so upkeep doesn't depend on someone noticing a problem.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="inlineStr"/>
-      <c r="H14" s="6" t="n">
+      <c r="G14" s="5" t="inlineStr"/>
+      <c r="H14" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I14" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>Reference materials with content upkeep challenge.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>R13</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
         <is>
           <t>Q2=C AND Q3=D</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C15" s="5" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D15" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr"/>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="E15" s="5" t="inlineStr"/>
+      <c r="F15" s="5" t="inlineStr">
         <is>
           <t>Link each microlearning resource to the task it supports, so people can apply it at work.</t>
         </is>
       </c>
-      <c r="G15" s="6" t="inlineStr"/>
-      <c r="H15" s="6" t="n">
+      <c r="G15" s="5" t="inlineStr"/>
+      <c r="H15" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I15" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J15" s="6" t="inlineStr">
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
         <is>
           <t>Microlearning with engagement challenge.</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>R14</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B16" s="5" t="inlineStr">
         <is>
           <t>Q2=B AND Q3=A</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C16" s="5" t="inlineStr">
         <is>
           <t>delivery</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D16" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr"/>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="E16" s="5" t="inlineStr"/>
+      <c r="F16" s="5" t="inlineStr">
         <is>
           <t>If live sessions take much of your team's time, consider which could be recorded or supported with self-paced material.</t>
         </is>
       </c>
-      <c r="G16" s="6" t="inlineStr"/>
-      <c r="H16" s="6" t="n">
+      <c r="G16" s="5" t="inlineStr"/>
+      <c r="H16" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I16" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J16" s="6" t="inlineStr">
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
         <is>
           <t>Capacity pressure with in-person delivery.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>R15</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B17" s="5" t="inlineStr">
         <is>
           <t>Q4=A AND Q5=A</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C17" s="5" t="inlineStr">
         <is>
           <t>sourcing</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D17" s="5" t="inlineStr">
         <is>
           <t>Replace</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr"/>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="E17" s="5" t="inlineStr"/>
+      <c r="F17" s="5" t="inlineStr">
         <is>
           <t>As learning is handled in-house without a dedicated team, it is likely spread across other roles. Agree a simple way to share templates and decisions between them.</t>
         </is>
       </c>
-      <c r="G17" s="6" t="inlineStr"/>
-      <c r="H17" s="6" t="n">
+      <c r="G17" s="5" t="inlineStr"/>
+      <c r="H17" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I17" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J17" s="6" t="inlineStr">
+      <c r="I17" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
         <is>
           <t>No dedicated team but in-house delivery: other internal roles do the work.</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>R16</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B18" s="5" t="inlineStr">
         <is>
           <t>Q4=A AND Q5=C</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C18" s="5" t="inlineStr">
         <is>
           <t>team</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D18" s="5" t="inlineStr">
         <is>
           <t>Replace</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr"/>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="E18" s="5" t="inlineStr"/>
+      <c r="F18" s="5" t="inlineStr">
         <is>
           <t>You don't have a dedicated internal L&amp;D team and partners deliver most of the work, so name an internal owner who sets priorities, briefs partners and signs off quality.</t>
         </is>
       </c>
-      <c r="G18" s="6" t="inlineStr"/>
-      <c r="H18" s="6" t="n">
+      <c r="G18" s="5" t="inlineStr"/>
+      <c r="H18" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I18" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J18" s="6" t="inlineStr">
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
         <is>
           <t>No internal team, partner-led delivery.</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="6" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>R17</t>
         </is>
       </c>
-      <c r="B19" s="6" t="inlineStr">
+      <c r="B19" s="5" t="inlineStr">
         <is>
           <t>Q4=D AND Q5=B</t>
         </is>
       </c>
-      <c r="C19" s="6" t="inlineStr">
+      <c r="C19" s="5" t="inlineStr">
         <is>
           <t>sourcing</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
+      <c r="D19" s="5" t="inlineStr">
         <is>
           <t>Replace</t>
         </is>
       </c>
-      <c r="E19" s="6" t="inlineStr"/>
-      <c r="F19" s="6" t="inlineStr">
+      <c r="E19" s="5" t="inlineStr"/>
+      <c r="F19" s="5" t="inlineStr">
         <is>
           <t>With a large team working alongside partners, clarify review ownership and quality standards across internal teams and partners, and keep one shared view of work in progress.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="inlineStr"/>
-      <c r="H19" s="6" t="n">
+      <c r="G19" s="5" t="inlineStr"/>
+      <c r="H19" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I19" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J19" s="6" t="inlineStr">
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>Large hybrid team.</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="6" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>R18</t>
         </is>
       </c>
-      <c r="B20" s="6" t="inlineStr">
+      <c r="B20" s="5" t="inlineStr">
         <is>
           <t>Q1=D AND Q6=E</t>
         </is>
       </c>
-      <c r="C20" s="6" t="inlineStr">
+      <c r="C20" s="5" t="inlineStr">
         <is>
           <t>priority_goal</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="5" t="inlineStr">
         <is>
           <t>Replace</t>
         </is>
       </c>
-      <c r="E20" s="6" t="inlineStr"/>
-      <c r="F20" s="6" t="inlineStr">
+      <c r="E20" s="5" t="inlineStr"/>
+      <c r="F20" s="5" t="inlineStr">
         <is>
           <t>Connect an existing learning measure to a relevant operational outcome, and agree with business owners how to evaluate the change.</t>
         </is>
       </c>
-      <c r="G20" s="6" t="inlineStr"/>
-      <c r="H20" s="6" t="n">
+      <c r="G20" s="5" t="inlineStr"/>
+      <c r="H20" s="5" t="n">
         <v>10</v>
       </c>
-      <c r="I20" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J20" s="6" t="inlineStr">
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
         <is>
           <t>Optimizing teams already measure; build on it rather than start from scratch.</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="6" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>R19</t>
         </is>
       </c>
-      <c r="B21" s="6" t="inlineStr">
+      <c r="B21" s="5" t="inlineStr">
         <is>
           <t>Q1=A AND Q6=E</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C21" s="5" t="inlineStr">
         <is>
           <t>next90</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="5" t="inlineStr">
         <is>
           <t>Add before</t>
         </is>
       </c>
-      <c r="E21" s="6" t="inlineStr"/>
-      <c r="F21" s="6" t="inlineStr">
+      <c r="E21" s="5" t="inlineStr"/>
+      <c r="F21" s="5" t="inlineStr">
         <is>
           <t>Start with one simple, agreed measure rather than a full evaluation framework.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="inlineStr"/>
-      <c r="H21" s="6" t="n">
+      <c r="G21" s="5" t="inlineStr"/>
+      <c r="H21" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J21" s="6" t="inlineStr">
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>Foundational teams seeking impact.</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>R20</t>
         </is>
       </c>
-      <c r="B22" s="6" t="inlineStr">
+      <c r="B22" s="5" t="inlineStr">
         <is>
           <t>Q1=A AND Q6=A</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C22" s="5" t="inlineStr">
         <is>
           <t>next90</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
+      <c r="D22" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E22" s="6" t="inlineStr"/>
-      <c r="F22" s="6" t="inlineStr">
+      <c r="E22" s="5" t="inlineStr"/>
+      <c r="F22" s="5" t="inlineStr">
         <is>
           <t>Keep the process simple: a shared request list and one template are enough to start.</t>
         </is>
       </c>
-      <c r="G22" s="6" t="inlineStr"/>
-      <c r="H22" s="6" t="n">
+      <c r="G22" s="5" t="inlineStr"/>
+      <c r="H22" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="6" t="inlineStr">
-        <is>
-          <t>In review</t>
-        </is>
-      </c>
-      <c r="J22" s="6" t="inlineStr">
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
         <is>
           <t>Foundational teams seeking capacity.</t>
         </is>

--- a/content/aptara-survey-content.xlsx
+++ b/content/aptara-survey-content.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Your answers are used only to generate your result. We don't ask for contact details unless you choose to share them.</t>
+          <t>Your answers stay in your browser and are used only to generate your result.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -846,11 +846,7 @@
           <t>lead_endpoint</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
-        <is>
-          <t>https://formsubmit.co/ajax/karthikeyan@aptaracorp.com</t>
-        </is>
-      </c>
+      <c r="B15" s="5" t="n"/>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Where follow-up requests are sent. Leave empty to hide the follow-up form.</t>

--- a/content/aptara-survey-content.xlsx
+++ b/content/aptara-survey-content.xlsx
@@ -760,7 +760,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Your answers stay in your browser and are used only to generate your result.</t>
+          <t>Your answers are used only to generate your result. We don't ask for contact details unless you choose to share them.</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -846,7 +846,11 @@
           <t>lead_endpoint</t>
         </is>
       </c>
-      <c r="B15" s="5" t="n"/>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>https://formsubmit.co/ajax/karthikeyan@aptaracorp.com</t>
+        </is>
+      </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
           <t>Where follow-up requests are sent. Leave empty to hide the follow-up form.</t>

--- a/content/aptara-survey-content.xlsx
+++ b/content/aptara-survey-content.xlsx
@@ -523,7 +523,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Rules: Remove hides a section; Replace, Add before and Add after change its text. See docs/recommendation-mapping.md in the repo.</t>
+          <t>Rules: Remove hides a section; Replace, Add before and Add after change its text. Only the highest-Priority rule of each mode applies to a section. Priority cards with the same Action are shown once. See docs/recommendation-mapping.md in the repo.</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2203,6 +2203,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="50" customWidth="1" min="7" max="7"/>
+    <col width="50" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1">
@@ -2248,6 +2249,11 @@
           <t>Writing guidance</t>
         </is>
       </c>
+      <c r="H2" s="4" t="inlineStr">
+        <is>
+          <t>Merge note</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="5" t="inlineStr">
@@ -2283,6 +2289,7 @@
           <t>Names the first priority, using the same words as its heading.</t>
         </is>
       </c>
+      <c r="H3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -2318,6 +2325,7 @@
           <t>Restates the stage they chose, in their terms. Directional, not a diagnosis.</t>
         </is>
       </c>
+      <c r="H4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2353,6 +2361,7 @@
           <t>Heading = the action. Text = what to do. Why = which answer it comes from.</t>
         </is>
       </c>
+      <c r="H5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2385,7 +2394,12 @@
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Heading = the action. Removed by a rule when it repeats the challenge priority.</t>
+          <t>Heading = the action. Merged into an earlier priority when it has the same Action tag.</t>
+        </is>
+      </c>
+      <c r="H6" s="5" t="inlineStr">
+        <is>
+          <t>It also supports the business goal you chose for the next 6–12 months.</t>
         </is>
       </c>
     </row>
@@ -2423,6 +2437,11 @@
           <t>The level of process and governance guidance that fits their stage.</t>
         </is>
       </c>
+      <c r="H7" s="5" t="inlineStr">
+        <is>
+          <t>It also fits the stage you described ({Q1}).</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2455,9 +2474,10 @@
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Single method: advice for that method. MULTI: advice for using several methods together; {Q3} lists them.</t>
-        </is>
-      </c>
+          <t>States the method mix only. A rule adds one sentence chosen by main challenge (and method, where it matters).</t>
+        </is>
+      </c>
+      <c r="H8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2485,33 +2505,34 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Context card (first sentence)</t>
+          <t>Context card</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Workload advice for their team size. Never assume an internal production team.</t>
-        </is>
-      </c>
+          <t>Replaced by a rule for each team size and sourcing pair, so team and sourcing read as one paragraph. These blocks are the fallback.</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>sourcing</t>
+          <t>next30</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Your team and capacity</t>
+          <t>Next 30 days</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="D10" s="5" t="n">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -2520,33 +2541,34 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Context card (second sentence)</t>
+          <t>Action</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Coordination advice for how work is delivered. Don't prescribe outsourcing.</t>
-        </is>
-      </c>
+          <t>One practical action for their main challenge that they can start this month.</t>
+        </is>
+      </c>
+      <c r="H10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>next30</t>
+          <t>next90</t>
         </is>
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Next 30 days</t>
+          <t>Next 90 days</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="D11" s="5" t="n">
-        <v>260</v>
+        <v>280</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -2560,48 +2582,14 @@
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>One practical action for their main challenge that they can start this month.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="inlineStr">
-        <is>
-          <t>next90</t>
-        </is>
-      </c>
-      <c r="B12" s="5" t="inlineStr">
-        <is>
-          <t>Next 90 days</t>
-        </is>
-      </c>
-      <c r="C12" s="5" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="D12" s="5" t="n">
-        <v>280</v>
-      </c>
-      <c r="E12" s="5" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr">
-        <is>
           <t>A feasible step toward their 6–12 month goal.</t>
         </is>
       </c>
+      <c r="H11" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2613,7 +2601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J48"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -2626,12 +2614,13 @@
     <col width="16" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1" ht="60" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>The text each answer contributes. Heading and 'Why this matters' are used by priority cards. For a Multi question, the MULTI row is used when more than one answer is selected. Mark Approved when reviewed.</t>
+          <t>The text each answer contributes. Heading and 'Why this matters' are used by priority cards. For a Multi question, the MULTI row is used when more than one answer is selected. Action names the central action of a priority card: when two priority cards share an Action, only the first is shown and the other's Merge note (Sections tab) is added to its reason. Mark Approved when reviewed.</t>
         </is>
       </c>
     </row>
@@ -2684,6 +2673,11 @@
       <c r="J2" s="4" t="inlineStr">
         <is>
           <t>Reviewer notes</t>
+        </is>
+      </c>
+      <c r="K2" s="4" t="inlineStr">
+        <is>
+          <t>Action</t>
         </is>
       </c>
     </row>
@@ -2725,6 +2719,7 @@
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr"/>
+      <c r="K3" s="5" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -2764,6 +2759,7 @@
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr"/>
+      <c r="K4" s="5" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
@@ -2803,6 +2799,7 @@
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr"/>
+      <c r="K5" s="5" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
@@ -2842,6 +2839,7 @@
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr"/>
+      <c r="K6" s="5" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -2881,6 +2879,7 @@
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr"/>
+      <c r="K7" s="5" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
@@ -2920,6 +2919,7 @@
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr"/>
+      <c r="K8" s="5" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
@@ -2959,6 +2959,7 @@
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="5" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -2998,6 +2999,7 @@
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr"/>
+      <c r="K10" s="5" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -3037,6 +3039,7 @@
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr"/>
+      <c r="K11" s="5" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -3066,7 +3069,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Identify your most-used and highest-risk content and review it first for outdated information, accessibility gaps and parts you could reuse. Give each item a review date so upkeep becomes routine.</t>
+          <t>List your most-used and highest-risk content, and give each item an owner and a review date, so upkeep becomes routine rather than something done only when a problem is noticed.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
@@ -3083,7 +3086,16 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J12" s="5" t="inlineStr"/>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="inlineStr">
+        <is>
+          <t>content-upkeep</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -3113,7 +3125,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Make demand visible in one backlog, agree how requests are prioritized, and build reusable templates and patterns so each new program takes less effort.</t>
+          <t>Make demand visible in one shared backlog and agree with stakeholders how requests are prioritized, so your team’s time goes to the work that matters most.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
@@ -3130,7 +3142,16 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="inlineStr">
+        <is>
+          <t>intake-prioritization</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -3178,6 +3199,11 @@
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="5" t="inlineStr">
+        <is>
+          <t>learner-application</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
@@ -3225,6 +3251,11 @@
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr"/>
+      <c r="K15" s="5" t="inlineStr">
+        <is>
+          <t>quality-governance</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -3272,6 +3303,11 @@
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr"/>
+      <c r="K16" s="5" t="inlineStr">
+        <is>
+          <t>impact-measurement</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -3301,7 +3337,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Look at where time goes today, from request to launch, and remove the biggest bottlenecks before adding more programs. Reusable designs and clear sign-off steps add capacity without adding people.</t>
+          <t>Look at where time goes from request to launch and remove the biggest bottlenecks, such as unclear sign-off or repeated rework, before adding more programs.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
@@ -3318,7 +3354,16 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr"/>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="inlineStr">
+        <is>
+          <t>workflow-bottlenecks</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -3366,6 +3411,11 @@
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr"/>
+      <c r="K18" s="5" t="inlineStr">
+        <is>
+          <t>reusable-production</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -3413,6 +3463,11 @@
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr"/>
+      <c r="K19" s="5" t="inlineStr">
+        <is>
+          <t>quality-governance</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
@@ -3460,6 +3515,11 @@
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr"/>
+      <c r="K20" s="5" t="inlineStr">
+        <is>
+          <t>learner-application</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -3507,6 +3567,11 @@
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr"/>
+      <c r="K21" s="5" t="inlineStr">
+        <is>
+          <t>impact-measurement</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
@@ -3554,6 +3619,11 @@
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr"/>
+      <c r="K22" s="5" t="inlineStr">
+        <is>
+          <t>intake-prioritization</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
@@ -3583,7 +3653,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Pick the processes and templates that work best today and make them the default for new programs, with a short checklist for design and review.</t>
+          <t>Pick the planning and build steps that work best today and make them the default way every new program is run, so results depend less on who does the work.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
@@ -3600,7 +3670,16 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr"/>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="inlineStr">
+        <is>
+          <t>standard-process</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="inlineStr">
@@ -3648,6 +3727,11 @@
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr"/>
+      <c r="K24" s="5" t="inlineStr">
+        <is>
+          <t>portfolio-focus</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
@@ -3695,6 +3779,11 @@
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr"/>
+      <c r="K25" s="5" t="inlineStr">
+        <is>
+          <t>scale-evidence</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -3720,7 +3809,7 @@
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>You deliver learning through in-person sessions. Consider which parts could be supported with short reference materials or follow-up activities, so learning continues after the session.</t>
+          <t>You deliver learning through in-person sessions.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr"/>
@@ -3733,7 +3822,12 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -3759,7 +3853,7 @@
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>You deliver learning through virtual live sessions. Keep sessions interactive and focused, and add simple follow-up materials so people can revisit key points.</t>
+          <t>You deliver learning through virtual live sessions.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr"/>
@@ -3772,7 +3866,12 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="5" t="inlineStr">
@@ -3798,7 +3897,7 @@
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>You use self-paced eLearning. Review your most-used modules regularly for outdated examples and accessibility gaps, and look for content you could reuse across courses.</t>
+          <t>You use self-paced eLearning.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr"/>
@@ -3811,7 +3910,12 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="5" t="inlineStr">
@@ -3837,7 +3941,7 @@
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>You use microlearning and performance support. Make sure each resource is easy to find at the moment of need, and link related resources so they support a bigger goal.</t>
+          <t>You use microlearning and performance support.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr"/>
@@ -3850,7 +3954,12 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="5" t="inlineStr">
@@ -3876,7 +3985,7 @@
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>You use documents and reference materials. Keep them current, easy to search and clearly owned, and consider which topics would benefit from practice or guided learning.</t>
+          <t>You use documents and reference materials.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr"/>
@@ -3889,7 +3998,12 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="5" t="inlineStr">
@@ -3915,7 +4029,7 @@
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>You use several delivery methods: {Q3}. Identify where they can work together to support the same outcome, rather than planning each one separately.</t>
+          <t>You use several delivery methods: {Q3}.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr"/>
@@ -3928,7 +4042,12 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -3968,6 +4087,7 @@
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr"/>
+      <c r="K32" s="5" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -4007,6 +4127,7 @@
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr"/>
+      <c r="K33" s="5" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="5" t="inlineStr">
@@ -4046,6 +4167,7 @@
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr"/>
+      <c r="K34" s="5" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -4085,16 +4207,17 @@
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr"/>
+      <c r="K35" s="5" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>sourcing</t>
+          <t>next30</t>
         </is>
       </c>
       <c r="B36" s="5" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
@@ -4104,13 +4227,13 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Mainly in-house: Mainly in-house, by our own people.</t>
+          <t>Content upkeep: Keeping existing learning content accurate, relevant and up to date.</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Because most work is done in-house, document key processes and decisions so knowledge isn't held by only a few people.</t>
+          <t>List your most-used learning assets and note when each was last reviewed. Pick the two most out of date and schedule their review.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr"/>
@@ -4124,16 +4247,17 @@
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr"/>
+      <c r="K36" s="5" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>sourcing</t>
+          <t>next30</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
@@ -4143,13 +4267,13 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Mixed: By a mix of our own people and external partners.</t>
+          <t>Delivery capacity: Producing and delivering learning fast enough to meet demand.</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>With work shared between your own people and partners, agree briefs, review steps and quality standards that both sides use.</t>
+          <t>Put every open learning request into one list with a requester, a deadline and a business reason, and agree the top priorities with stakeholders.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr"/>
@@ -4163,16 +4287,17 @@
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr"/>
+      <c r="K37" s="5" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>sourcing</t>
+          <t>next30</t>
         </is>
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>Q5</t>
+          <t>Q2</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
@@ -4182,13 +4307,13 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Mainly partners: Mainly by external partners.</t>
+          <t>Learner engagement: Getting people to take part in learning and apply it at work.</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>As partners deliver most of the work, keep ownership of priorities, quality standards and final sign-off inside your organization.</t>
+          <t>Ask a few recent participants and their managers what they have used at work since the program, and note what got in the way.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr"/>
@@ -4202,6 +4327,7 @@
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr"/>
+      <c r="K38" s="5" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
@@ -4216,18 +4342,18 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Content upkeep: Keeping existing learning content accurate, relevant and up to date.</t>
+          <t>Consistent quality: Keeping quality consistent across programs, teams or regions.</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>List your most-used learning assets and note when each was last reviewed. Pick the two most out of date and schedule their review.</t>
+          <t>Draft a one-page quality checklist and test it on two recent programs, ideally built by different people or partners.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr"/>
@@ -4241,6 +4367,7 @@
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr"/>
+      <c r="K39" s="5" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -4255,18 +4382,18 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Delivery capacity: Producing and delivering learning fast enough to meet demand.</t>
+          <t>Demonstrating impact: Showing how learning contributes to business results.</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Put every open learning request into one list with a requester, a deadline and a business reason, and agree the top priorities with stakeholders.</t>
+          <t>Pick one priority program and agree with its business owner which measure it should influence and where the data will come from.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr"/>
@@ -4280,32 +4407,33 @@
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr"/>
+      <c r="K40" s="5" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>next30</t>
+          <t>next90</t>
         </is>
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>A</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Learner engagement: Getting people to take part in learning and apply it at work.</t>
+          <t>Delivery capacity: Increase delivery capacity.</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Ask a few recent participants and their managers what they have used at work since the program, and note what got in the way.</t>
+          <t>Map how a typical program moves from request to launch, remove the biggest bottleneck, and agree clear sign-off steps for your most common requests.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr"/>
@@ -4318,33 +4446,38 @@
           <t>Approved</t>
         </is>
       </c>
-      <c r="J41" s="5" t="inlineStr"/>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>Updated 2026-10-11 (follow-up polish)</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>next30</t>
+          <t>next90</t>
         </is>
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>B</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Consistent quality: Keeping quality consistent across programs, teams or regions.</t>
+          <t>Faster development: Reduce development and update time.</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Draft a one-page quality checklist and test it on two recent programs, ideally built by different people or partners.</t>
+          <t>Build a shared library of templates and reusable components, and organize source files so any program can be updated quickly.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr"/>
@@ -4358,32 +4491,33 @@
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr"/>
+      <c r="K42" s="5" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>next30</t>
+          <t>next90</t>
         </is>
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>Q2</t>
+          <t>Q6</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>C</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Demonstrating impact: Showing how learning contributes to business results.</t>
+          <t>Quality and consistency: Improve learning quality and consistency.</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Pick one priority program and agree with its business owner which measure it should influence and where the data will come from.</t>
+          <t>Roll out a quality checklist to everyone who builds or reviews learning, and review a sample of programs against it at the end of the quarter.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr"/>
@@ -4397,6 +4531,7 @@
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr"/>
+      <c r="K43" s="5" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -4411,18 +4546,18 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Delivery capacity: Increase delivery capacity.</t>
+          <t>Engagement and application: Improve learner engagement and application.</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Map how a typical program moves from request to launch, remove the biggest bottleneck, and create reusable templates for your most common requests.</t>
+          <t>Redesign one program with practice activities and manager follow-up, then compare participation, feedback and application with the previous version.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr"/>
@@ -4436,6 +4571,7 @@
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr"/>
+      <c r="K44" s="5" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -4450,18 +4586,18 @@
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>E</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Faster development: Reduce development and update time.</t>
+          <t>Business impact: Demonstrate business impact.</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Build a shared library of templates and reusable components, and organize source files so any program can be updated quickly.</t>
+          <t>Share the results of one evaluated program with its business owner, agree what the evidence does and doesn't show, and decide which program to evaluate next.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr"/>
@@ -4475,127 +4611,11 @@
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr"/>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>next90</t>
-        </is>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>Quality and consistency: Improve learning quality and consistency.</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>Roll out a quality checklist to everyone who builds or reviews learning, and review a sample of programs against it at the end of the quarter.</t>
-        </is>
-      </c>
-      <c r="G46" s="5" t="inlineStr"/>
-      <c r="H46" s="5">
-        <f>LEN(F46)</f>
-        <v/>
-      </c>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J46" s="5" t="inlineStr"/>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>next90</t>
-        </is>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>Engagement and application: Improve learner engagement and application.</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Redesign one program with practice activities and manager follow-up, then compare participation, feedback and application with the previous version.</t>
-        </is>
-      </c>
-      <c r="G47" s="5" t="inlineStr"/>
-      <c r="H47" s="5">
-        <f>LEN(F47)</f>
-        <v/>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J47" s="5" t="inlineStr"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>next90</t>
-        </is>
-      </c>
-      <c r="B48" s="5" t="inlineStr">
-        <is>
-          <t>Q6</t>
-        </is>
-      </c>
-      <c r="C48" s="5" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="D48" s="5" t="inlineStr">
-        <is>
-          <t>Business impact: Demonstrate business impact.</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="inlineStr"/>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>Share the results of one evaluated program with its business owner, agree what the evidence does and doesn't show, and decide which program to evaluate next.</t>
-        </is>
-      </c>
-      <c r="G48" s="5" t="inlineStr"/>
-      <c r="H48" s="5">
-        <f>LEN(F48)</f>
-        <v/>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J48" s="5" t="inlineStr"/>
+      <c r="K45" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:K1"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation sqref="I3:I500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
@@ -4612,7 +4632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4630,7 +4650,7 @@
     <row r="1" ht="60" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>Overrides for specific combinations. 'When' uses Q-code=answer pairs joined by AND (for a Multi question, Q3=C means C is among the selections). Modes: Replace, Add before, Add after, Remove (hides the section). Higher Priority wins when two Replace rules hit the same section.</t>
+          <t>Overrides for specific combinations. 'When' uses Q-code=answer pairs joined by AND (for a Multi question, Q3=C means C is among the selections). Modes: Replace, Add before, Add after, Remove (hides the section). When several rules of the same mode match a section, only the one with the highest Priority applies (ties: the higher row).</t>
         </is>
       </c>
     </row>
@@ -4694,22 +4714,26 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>Q2=A AND Q6=B</t>
+          <t>Q4=A AND Q5=A</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>priority_goal</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Remove</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="inlineStr"/>
-      <c r="F3" s="5" t="inlineStr"/>
-      <c r="G3" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="5" t="inlineStr">
+        <is>
+          <t>Without a dedicated L&amp;D team, learning is likely handled by people in other roles. Agree who decides priorities and signs off content, and share simple templates so no one starts from scratch.</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="n"/>
       <c r="H3" s="5" t="n">
         <v>10</v>
       </c>
@@ -4720,7 +4744,7 @@
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Content upkeep and faster updates are the same priority; show it once.</t>
+          <t>No dedicated team + mainly in-house: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -4732,28 +4756,28 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>Q2=A AND Q6=B</t>
+          <t>Q4=A AND Q5=B</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>priority_challenge</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Add after</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>This is also the goal you set for the next 6–12 months, so it is listed once.</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr"/>
+          <t>Without a dedicated L&amp;D team, name an internal owner who decides priorities and signs off content, and give partners clear briefs so internal and external work fits together.</t>
+        </is>
+      </c>
+      <c r="G4" s="5" t="n"/>
       <c r="H4" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
@@ -4762,7 +4786,7 @@
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Explains why the goal priority is missing.</t>
+          <t>No dedicated team + mixed sourcing: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -4774,22 +4798,26 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>Q2=B AND Q6=A</t>
+          <t>Q4=A AND Q5=C</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>priority_goal</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Remove</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="inlineStr"/>
-      <c r="F5" s="5" t="inlineStr"/>
-      <c r="G5" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="5" t="inlineStr">
+        <is>
+          <t>Name an internal owner to prioritize requests, brief partners and approve quality. Use a simple shared tracker to keep delivery visible.</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="n"/>
       <c r="H5" s="5" t="n">
         <v>10</v>
       </c>
@@ -4800,7 +4828,7 @@
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Delivery capacity challenge and goal are the same priority.</t>
+          <t>No dedicated team + mainly partners: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -4812,28 +4840,28 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>Q2=B AND Q6=A</t>
+          <t>Q4=B AND Q5=A</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>priority_challenge</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Add after</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>This is also the goal you set for the next 6–12 months, so it is listed once.</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr"/>
+          <t>Protect limited capacity with a prioritized backlog, reusable templates and documented handoffs, so work doesn’t depend on one person.</t>
+        </is>
+      </c>
+      <c r="G6" s="5" t="n"/>
       <c r="H6" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
@@ -4842,7 +4870,7 @@
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Explains why the goal priority is missing.</t>
+          <t>Small team + mainly in-house: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -4854,22 +4882,26 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Q2=C AND Q6=D</t>
+          <t>Q4=B AND Q5=B</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>priority_goal</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Remove</t>
-        </is>
-      </c>
-      <c r="E7" s="5" t="inlineStr"/>
-      <c r="F7" s="5" t="inlineStr"/>
-      <c r="G7" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="inlineStr">
+        <is>
+          <t>With a small team working alongside partners, keep one prioritized backlog and decide early which work partners take on, with clear briefs and one shared review step.</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="n"/>
       <c r="H7" s="5" t="n">
         <v>10</v>
       </c>
@@ -4880,7 +4912,7 @@
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Engagement challenge and goal are the same priority.</t>
+          <t>Small team + mixed sourcing: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -4892,28 +4924,28 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>Q2=C AND Q6=D</t>
+          <t>Q4=B AND Q5=C</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>priority_challenge</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Add after</t>
-        </is>
-      </c>
-      <c r="E8" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>This is also the goal you set for the next 6–12 months, so it is listed once.</t>
-        </is>
-      </c>
-      <c r="G8" s="5" t="inlineStr"/>
+          <t>With a small team and partners doing most of the work, focus your team on prioritizing requests, briefing partners and approving quality rather than on production.</t>
+        </is>
+      </c>
+      <c r="G8" s="5" t="n"/>
       <c r="H8" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
@@ -4922,7 +4954,7 @@
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Explains why the goal priority is missing.</t>
+          <t>Small team + mainly partners: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -4934,22 +4966,26 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Q2=D AND Q6=C</t>
+          <t>Q4=C AND Q5=A</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>priority_goal</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Remove</t>
-        </is>
-      </c>
-      <c r="E9" s="5" t="inlineStr"/>
-      <c r="F9" s="5" t="inlineStr"/>
-      <c r="G9" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="5" t="inlineStr">
+        <is>
+          <t>With a medium-sized team working in-house, agree shared standards and documented handoffs so work stays consistent as it moves between people.</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="n"/>
       <c r="H9" s="5" t="n">
         <v>10</v>
       </c>
@@ -4960,7 +4996,7 @@
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Quality challenge and goal are the same priority.</t>
+          <t>Medium team + mainly in-house: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -4972,28 +5008,28 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Q2=D AND Q6=C</t>
+          <t>Q4=C AND Q5=B</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>priority_challenge</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Add after</t>
-        </is>
-      </c>
-      <c r="E10" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>This is also the goal you set for the next 6–12 months, so it is listed once.</t>
-        </is>
-      </c>
-      <c r="G10" s="5" t="inlineStr"/>
+          <t>Agree clear briefs, review responsibilities and handoffs across your team and partners so work stays consistent.</t>
+        </is>
+      </c>
+      <c r="G10" s="5" t="n"/>
       <c r="H10" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
@@ -5002,7 +5038,7 @@
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Explains why the goal priority is missing.</t>
+          <t>Medium team + mixed sourcing: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -5014,22 +5050,26 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>Q2=E AND Q6=E</t>
+          <t>Q4=C AND Q5=C</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>priority_goal</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Remove</t>
-        </is>
-      </c>
-      <c r="E11" s="5" t="inlineStr"/>
-      <c r="F11" s="5" t="inlineStr"/>
-      <c r="G11" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="5" t="inlineStr">
+        <is>
+          <t>With partners delivering most of the work, use your team to set standards, brief partners and review what comes back, so quality stays consistent across suppliers.</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="n"/>
       <c r="H11" s="5" t="n">
         <v>10</v>
       </c>
@@ -5040,7 +5080,7 @@
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Impact challenge and goal are the same priority.</t>
+          <t>Medium team + mainly partners: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -5052,28 +5092,28 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>Q2=E AND Q6=E</t>
+          <t>Q4=D AND Q5=A</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>priority_challenge</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Add after</t>
-        </is>
-      </c>
-      <c r="E12" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>This is also the goal you set for the next 6–12 months, so it is listed once.</t>
-        </is>
-      </c>
-      <c r="G12" s="5" t="inlineStr"/>
+          <t>With a large in-house team, make roles and review ownership clear across groups and keep one view of work in progress, so effort isn’t duplicated.</t>
+        </is>
+      </c>
+      <c r="G12" s="5" t="n"/>
       <c r="H12" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
@@ -5082,7 +5122,7 @@
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Explains why the goal priority is missing.</t>
+          <t>Large team + mainly in-house: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -5094,28 +5134,28 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>Q2=A AND Q3=C</t>
+          <t>Q4=D AND Q5=B</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>delivery</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Add after</t>
-        </is>
-      </c>
-      <c r="E13" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>As content upkeep is your main challenge, start with your highest-use eLearning: check for outdated examples, accessibility gaps and reusable content.</t>
-        </is>
-      </c>
-      <c r="G13" s="5" t="inlineStr"/>
+          <t>With a large team working alongside partners, agree shared quality standards, assign review and sign-off owners, and maintain one view of work in progress.</t>
+        </is>
+      </c>
+      <c r="G13" s="5" t="n"/>
       <c r="H13" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
@@ -5124,7 +5164,7 @@
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>eLearning user with content upkeep challenge.</t>
+          <t>Large team + mixed sourcing: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -5136,28 +5176,28 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>Q2=A AND Q3=E</t>
+          <t>Q4=D AND Q5=C</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>delivery</t>
+          <t>team</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Add after</t>
-        </is>
-      </c>
-      <c r="E14" s="5" t="inlineStr"/>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Give each reference document an owner and a review date, so upkeep doesn't depend on someone noticing a problem.</t>
-        </is>
-      </c>
-      <c r="G14" s="5" t="inlineStr"/>
+          <t>With a large team and partners delivering most of the work, give each partner relationship a clear owner and apply the same standards and sign-off to all of them.</t>
+        </is>
+      </c>
+      <c r="G14" s="5" t="n"/>
       <c r="H14" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
@@ -5166,7 +5206,7 @@
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Reference materials with content upkeep challenge.</t>
+          <t>Large team + mainly partners: one paragraph covering team size and sourcing together.</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5218,7 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>Q2=C AND Q3=D</t>
+          <t>Q2=A</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -5191,15 +5231,15 @@
           <t>Add after</t>
         </is>
       </c>
-      <c r="E15" s="5" t="inlineStr"/>
+      <c r="E15" s="5" t="n"/>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Link each microlearning resource to the task it supports, so people can apply it at work.</t>
-        </is>
-      </c>
-      <c r="G15" s="5" t="inlineStr"/>
+          <t>Start with your highest-use materials in each format and check them for outdated information, accessibility gaps and parts you could reuse.</t>
+        </is>
+      </c>
+      <c r="G15" s="5" t="n"/>
       <c r="H15" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
@@ -5208,7 +5248,7 @@
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Microlearning with engagement challenge.</t>
+          <t>Content upkeep: delivery advice that serves the main challenge, whatever the method mix.</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5260,7 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>Q2=B AND Q3=A</t>
+          <t>Q2=B</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -5233,15 +5273,15 @@
           <t>Add after</t>
         </is>
       </c>
-      <c r="E16" s="5" t="inlineStr"/>
+      <c r="E16" s="5" t="n"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>If live sessions take much of your team's time, consider which could be recorded or supported with self-paced material.</t>
-        </is>
-      </c>
-      <c r="G16" s="5" t="inlineStr"/>
+          <t>Look for content you rebuild for each request and turn it into reusable assets, so new work takes less effort whatever the format.</t>
+        </is>
+      </c>
+      <c r="G16" s="5" t="n"/>
       <c r="H16" s="5" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
@@ -5250,7 +5290,7 @@
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Capacity pressure with in-person delivery.</t>
+          <t>Delivery capacity: delivery advice that serves the main challenge, whatever the method mix.</t>
         </is>
       </c>
     </row>
@@ -5262,26 +5302,26 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Q4=A AND Q5=A</t>
+          <t>Q2=C</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>sourcing</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>Replace</t>
-        </is>
-      </c>
-      <c r="E17" s="5" t="inlineStr"/>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n"/>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>As learning is handled in-house without a dedicated team, it is likely spread across other roles. Agree a simple way to share templates and decisions between them.</t>
-        </is>
-      </c>
-      <c r="G17" s="5" t="inlineStr"/>
+          <t>Plan practice, participation and follow-up so people apply what they learn, rather than counting attendance or completion alone.</t>
+        </is>
+      </c>
+      <c r="G17" s="5" t="n"/>
       <c r="H17" s="5" t="n">
         <v>10</v>
       </c>
@@ -5292,7 +5332,7 @@
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>No dedicated team but in-house delivery: other internal roles do the work.</t>
+          <t>Learner engagement: delivery advice that serves the main challenge, whatever the method mix.</t>
         </is>
       </c>
     </row>
@@ -5304,26 +5344,26 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>Q4=A AND Q5=C</t>
+          <t>Q2=D</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>team</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>Replace</t>
-        </is>
-      </c>
-      <c r="E18" s="5" t="inlineStr"/>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>You don't have a dedicated internal L&amp;D team and partners deliver most of the work, so name an internal owner who sets priorities, briefs partners and signs off quality.</t>
-        </is>
-      </c>
-      <c r="G18" s="5" t="inlineStr"/>
+          <t>Apply the same quality and accessibility criteria to every format you use, with a few checks specific to each one.</t>
+        </is>
+      </c>
+      <c r="G18" s="5" t="n"/>
       <c r="H18" s="5" t="n">
         <v>10</v>
       </c>
@@ -5334,7 +5374,7 @@
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>No internal team, partner-led delivery.</t>
+          <t>Consistent quality: delivery advice that serves the main challenge, whatever the method mix.</t>
         </is>
       </c>
     </row>
@@ -5346,26 +5386,26 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Q4=D AND Q5=B</t>
+          <t>Q2=E</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>sourcing</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>Replace</t>
-        </is>
-      </c>
-      <c r="E19" s="5" t="inlineStr"/>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n"/>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>With a large team working alongside partners, clarify review ownership and quality standards across internal teams and partners, and keep one shared view of work in progress.</t>
-        </is>
-      </c>
-      <c r="G19" s="5" t="inlineStr"/>
+          <t>For one priority program, choose a measure of application or performance and agree a baseline with its business owner. Attendance and completion figures alone won’t show impact.</t>
+        </is>
+      </c>
+      <c r="G19" s="5" t="n"/>
       <c r="H19" s="5" t="n">
         <v>10</v>
       </c>
@@ -5376,7 +5416,7 @@
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Large hybrid team.</t>
+          <t>Demonstrating impact: delivery advice that serves the main challenge, whatever the method mix.</t>
         </is>
       </c>
     </row>
@@ -5388,28 +5428,28 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>Q1=D AND Q6=E</t>
+          <t>Q2=E AND Q3=C</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>priority_goal</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Replace</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="inlineStr"/>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Connect an existing learning measure to a relevant operational outcome, and agree with business owners how to evaluate the change.</t>
-        </is>
-      </c>
-      <c r="G20" s="5" t="inlineStr"/>
+          <t>For your eLearning, choose a meaningful application or performance measure, agree a baseline with the business owner, and connect module activity to what changes at work. Completions alone won’t prove impact.</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n"/>
       <c r="H20" s="5" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
@@ -5418,7 +5458,7 @@
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Optimizing teams already measure; build on it rather than start from scratch.</t>
+          <t>Impact + eLearning: measurement, not module upkeep.</t>
         </is>
       </c>
     </row>
@@ -5430,28 +5470,28 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>Q1=A AND Q6=E</t>
+          <t>Q2=A AND Q3=C</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>next90</t>
+          <t>delivery</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Add before</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr"/>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Start with one simple, agreed measure rather than a full evaluation framework.</t>
-        </is>
-      </c>
-      <c r="G21" s="5" t="inlineStr"/>
+          <t>Start with your highest-use eLearning modules: check them for obsolete examples, accessibility gaps and content you could reuse across courses.</t>
+        </is>
+      </c>
+      <c r="G21" s="5" t="n"/>
       <c r="H21" s="5" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
@@ -5460,7 +5500,7 @@
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Foundational teams seeking impact.</t>
+          <t>Content upkeep + eLearning.</t>
         </is>
       </c>
     </row>
@@ -5472,35 +5512,413 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
+          <t>Q2=A AND Q3=E</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>delivery</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="inlineStr">
+        <is>
+          <t>Keep reference documents in one place with a visible last-reviewed date, so people can trust what they find.</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n"/>
+      <c r="H22" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J22" s="5" t="inlineStr">
+        <is>
+          <t>Content upkeep + reference materials (eLearning wins if both are selected).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>R21</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Q2=C AND Q3=A</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>delivery</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="5" t="inlineStr">
+        <is>
+          <t>In live sessions, build in practice, discussion and feedback, and plan a follow-up activity so people apply what they learned rather than just attend.</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="n"/>
+      <c r="H23" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
+        <is>
+          <t>Engagement + in-person ILT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>R22</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Q2=C AND Q3=B</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>delivery</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="inlineStr">
+        <is>
+          <t>In live sessions, build in practice, discussion and feedback, and plan a follow-up activity so people apply what they learned rather than just attend.</t>
+        </is>
+      </c>
+      <c r="G24" s="5" t="n"/>
+      <c r="H24" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>Engagement + virtual ILT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>R23</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Q2=C AND Q3=D</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>delivery</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="inlineStr">
+        <is>
+          <t>Link each microlearning resource to the task it supports, so people can find it and apply it at the moment of need.</t>
+        </is>
+      </c>
+      <c r="G25" s="5" t="n"/>
+      <c r="H25" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>Engagement + microlearning (live sessions win if both are selected).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>R24</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Q2=B AND Q3=A</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>delivery</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="inlineStr">
+        <is>
+          <t>Identify session content you repeat often and turn it into reusable facilitation assets, reference materials or optional self-paced support, so live time goes where it adds most.</t>
+        </is>
+      </c>
+      <c r="G26" s="5" t="n"/>
+      <c r="H26" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Capacity + in-person ILT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>R25</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Q2=B AND Q3=B</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>delivery</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="5" t="inlineStr">
+        <is>
+          <t>Identify session content you repeat often and turn it into reusable facilitation assets, reference materials or optional self-paced support, so live time goes where it adds most.</t>
+        </is>
+      </c>
+      <c r="G27" s="5" t="n"/>
+      <c r="H27" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Capacity + virtual ILT.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>R26</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Q2=B AND Q6=B</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>delivery</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>Add after</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="5" t="inlineStr">
+        <is>
+          <t>Reuse approved source content and design patterns across your formats, and keep clear ownership and version control so updates are quick.</t>
+        </is>
+      </c>
+      <c r="G28" s="5" t="n"/>
+      <c r="H28" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Capacity challenge + faster development goal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>R27</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Q1=D AND Q6=E</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>priority_goal</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>Replace</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="5" t="inlineStr">
+        <is>
+          <t>Connect an existing learning measure to a relevant operational outcome, and agree with business owners how to evaluate the change.</t>
+        </is>
+      </c>
+      <c r="G29" s="5" t="n"/>
+      <c r="H29" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Optimizing teams already measure; build on it rather than start from scratch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
+        <is>
+          <t>R28</t>
+        </is>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Q1=A AND Q6=E</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>next90</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>Add before</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="5" t="inlineStr">
+        <is>
+          <t>Start with one simple, agreed measure rather than a full evaluation framework.</t>
+        </is>
+      </c>
+      <c r="G30" s="5" t="n"/>
+      <c r="H30" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Foundational teams seeking impact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>R29</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
           <t>Q1=A AND Q6=A</t>
         </is>
       </c>
-      <c r="C22" s="5" t="inlineStr">
+      <c r="C31" s="5" t="inlineStr">
         <is>
           <t>next90</t>
         </is>
       </c>
-      <c r="D22" s="5" t="inlineStr">
+      <c r="D31" s="5" t="inlineStr">
         <is>
           <t>Add after</t>
         </is>
       </c>
-      <c r="E22" s="5" t="inlineStr"/>
-      <c r="F22" s="5" t="inlineStr">
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="inlineStr">
         <is>
           <t>Keep the process simple: a shared request list and one template are enough to start.</t>
         </is>
       </c>
-      <c r="G22" s="5" t="inlineStr"/>
-      <c r="H22" s="5" t="n">
+      <c r="G31" s="5" t="n"/>
+      <c r="H31" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>Approved</t>
-        </is>
-      </c>
-      <c r="J22" s="5" t="inlineStr">
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>Foundational teams seeking capacity.</t>
         </is>
